--- a/member_deposit/2026-08-17_会员沉淀分析.xlsx
+++ b/member_deposit/2026-08-17_会员沉淀分析.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,14 +452,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23736</v>
+        <v>23746</v>
       </c>
       <c r="C2" t="n">
-        <v>23698</v>
+        <v>23708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+216</t>
+          <t>+226</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -515,14 +515,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70369</v>
+        <v>70393</v>
       </c>
       <c r="C5" t="n">
-        <v>70333</v>
+        <v>70357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+494</t>
+          <t>+518</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -574,72 +574,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>（未匹配门店）</t>
+          <t>未消费会员</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34</v>
+        <v>13114</v>
       </c>
       <c r="C8" t="n">
-        <v>34</v>
+        <v>12964</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+39</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>13075</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>未消费会员</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13114</v>
+        <v>209564</v>
       </c>
       <c r="C9" t="n">
-        <v>12964</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+39</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>13075</v>
-      </c>
+        <v>209335</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>剔除-门店标记剔除（不计入）</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>209564</v>
-      </c>
-      <c r="C10" t="n">
-        <v>209335</v>
-      </c>
+        <v>13279</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>剔除-门店标记剔除（不计入）</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>13279</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -652,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,26 +644,6 @@
         <is>
           <t>记录数</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DJI北京双安商场授权体验店</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DJI上海徐汇万科广场授权体验店</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -731,11 +690,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DJI上海FFC滨江悅里授权体验店</t>
+          <t>DJI上海徐汇万科广场授权体验店</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -749,11 +708,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海FFC滨江悅里授权体验店</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -767,11 +726,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DJI上海天荟广场授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>167</v>
+        <v>57</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -785,11 +744,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>DJI上海天荟广场授权体验店</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>452</v>
+        <v>167</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -803,11 +762,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DJI上海百联南桥购物中心授权体验店</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>481</v>
+        <v>452</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1001,11 +960,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DJI北京北投新奥天虹授权体验店</t>
+          <t>DJI北京双安商场授权体验店</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>267</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1019,11 +978,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DJI北京龙湖长安天街授权体验店</t>
+          <t>DJI北京北投新奥天虹授权体验店</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>344</v>
+        <v>267</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1037,11 +996,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DJI北京万柳华联授权体验店</t>
+          <t>DJI北京龙湖长安天街授权体验店</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>404</v>
+        <v>344</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1055,11 +1014,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DJI北京龙湖熙悦天街授权体验店</t>
+          <t>DJI北京万柳华联授权体验店</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1073,11 +1032,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DJI北京首都机场授权体验店</t>
+          <t>DJI北京龙湖熙悦天街授权体验店</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>526</v>
+        <v>428</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
